--- a/data/trans_orig/IP05A06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP05A06-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33830</t>
+          <t>33831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44076</t>
+          <t>43901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56711</t>
+          <t>56188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74419</t>
+          <t>74391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,3%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27846</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27726</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34896</t>
+          <t>35330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52148</t>
+          <t>53074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>16533</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67314</t>
+          <t>67051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82260</t>
+          <t>81762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63537</t>
+          <t>64137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80033</t>
+          <t>80488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136778</t>
+          <t>135621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158351</t>
+          <t>156933</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>72,93%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>21627</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35936</t>
+          <t>36896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>41820</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50845</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72615</t>
+          <t>72399</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45862</t>
+          <t>45272</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57321</t>
+          <t>57032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54336</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64534</t>
+          <t>64358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103970</t>
+          <t>103709</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119957</t>
+          <t>118750</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33691</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48553</t>
+          <t>48565</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62013</t>
+          <t>61348</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45629</t>
+          <t>45419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>59889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98556</t>
+          <t>98303</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>117602</t>
+          <t>118873</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>25109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>33430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52701</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31918</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46864</t>
+          <t>47141</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62207</t>
+          <t>62309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19613</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36713</t>
+          <t>36968</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34862</t>
+          <t>35979</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>46670</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>42470</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52942</t>
+          <t>52683</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>81885</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>96582</t>
+          <t>97380</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>19265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18450</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33173</t>
+          <t>32946</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>95699</t>
+          <t>95018</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>111877</t>
+          <t>112321</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106494</t>
+          <t>106204</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>121978</t>
+          <t>121967</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>206169</t>
+          <t>207624</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>230884</t>
+          <t>230773</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>39516</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20556</t>
+          <t>20454</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35899</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47202</t>
+          <t>47428</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71012</t>
+          <t>69923</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>106849</t>
+          <t>107672</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>126170</t>
+          <t>126654</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>116101</t>
+          <t>117902</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>135812</t>
+          <t>136684</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>229889</t>
+          <t>230481</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>256444</t>
+          <t>256868</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>35218</t>
+          <t>34850</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>54648</t>
+          <t>53532</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>33573</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>52612</t>
+          <t>51495</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>74161</t>
+          <t>74503</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>100729</t>
+          <t>99387</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>481977</t>
+          <t>480324</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>522132</t>
+          <t>519340</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>521058</t>
+          <t>521551</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>561508</t>
+          <t>560616</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1012527</t>
+          <t>1013972</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1071009</t>
+          <t>1072720</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>165609</t>
+          <t>167126</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>203476</t>
+          <t>205417</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>165371</t>
+          <t>165931</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>205451</t>
+          <t>205967</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>345253</t>
+          <t>344436</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>400772</t>
+          <t>400251</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>31790</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>33583</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>53786</t>
+          <t>54020</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38105</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29532</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42372</t>
+          <t>42149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59598</t>
+          <t>59634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77264</t>
+          <t>77058</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>17210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29197</t>
+          <t>29538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37476</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54626</t>
+          <t>53529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66263</t>
+          <t>66451</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80733</t>
+          <t>80486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71401</t>
+          <t>70625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86314</t>
+          <t>86196</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141413</t>
+          <t>141674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162472</t>
+          <t>163244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31570</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>18678</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33447</t>
+          <t>33304</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40552</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60140</t>
+          <t>59951</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,82 +5769,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10595</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>12460</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>18566</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5688</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2761</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11154</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12460</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7751</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>18749</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47931</t>
+          <t>48377</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59520</t>
+          <t>59074</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48945</t>
+          <t>49039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59617</t>
+          <t>59608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100460</t>
+          <t>100423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116217</t>
+          <t>116121</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18886</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34430</t>
+          <t>34941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48756</t>
+          <t>48084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61784</t>
+          <t>61069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56258</t>
+          <t>55794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67675</t>
+          <t>68346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108692</t>
+          <t>109379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126195</t>
+          <t>127237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,44%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>18046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36438</t>
+          <t>35685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31064</t>
+          <t>30173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39180</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31360</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40109</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65340</t>
+          <t>65268</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77937</t>
+          <t>77252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52246</t>
+          <t>52307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47823</t>
+          <t>48327</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55528</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>96085</t>
+          <t>96632</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>106371</t>
+          <t>106486</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>74812</t>
+          <t>75314</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93303</t>
+          <t>94136</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>84109</t>
+          <t>84603</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>102762</t>
+          <t>103208</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>166481</t>
+          <t>165820</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192414</t>
+          <t>191479</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,51%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>37877</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56985</t>
+          <t>56399</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35258</t>
+          <t>34656</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>52487</t>
+          <t>52108</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>77567</t>
+          <t>78395</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>103133</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>135751</t>
+          <t>135543</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>149493</t>
+          <t>149427</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>141459</t>
+          <t>141566</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>155654</t>
+          <t>155659</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>283002</t>
+          <t>282275</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>302523</t>
+          <t>302063</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>23320</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26541</t>
+          <t>26848</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>27117</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>45235</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>509154</t>
+          <t>510973</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>544977</t>
+          <t>547347</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>547125</t>
+          <t>545335</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>583631</t>
+          <t>583776</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1067061</t>
+          <t>1067112</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1119577</t>
+          <t>1120447</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>131602</t>
+          <t>130626</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>166175</t>
+          <t>164966</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>130923</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>165223</t>
+          <t>166622</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>273079</t>
+          <t>272046</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>322383</t>
+          <t>322596</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>32281</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>36990</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>64542</t>
+          <t>65249</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66723</t>
+          <t>66800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72787</t>
+          <t>72768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69757</t>
+          <t>69293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77514</t>
+          <t>77534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140293</t>
+          <t>139933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>149531</t>
+          <t>149467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37911</t>
+          <t>36197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105706</t>
+          <t>104173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95893</t>
+          <t>95895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112853</t>
+          <t>112136</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112803</t>
+          <t>121954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>211699</t>
+          <t>211026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26833</t>
+          <t>26522</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24103</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52913</t>
+          <t>51807</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81754</t>
+          <t>83093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117399</t>
+          <t>105833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47475</t>
+          <t>47858</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55074</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49851</t>
+          <t>49828</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59944</t>
+          <t>60273</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100164</t>
+          <t>100548</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113562</t>
+          <t>113330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>52823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64014</t>
+          <t>64047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62556</t>
+          <t>62498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75489</t>
+          <t>75247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119431</t>
+          <t>119480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136680</t>
+          <t>136905</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15894</t>
+          <t>16505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>25007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>809</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33493</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>34842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66200</t>
+          <t>66325</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72897</t>
+          <t>72864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37758</t>
+          <t>37466</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>41557</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52304</t>
+          <t>52244</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82513</t>
+          <t>82948</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95150</t>
+          <t>95155</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>360</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78811</t>
+          <t>79463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96230</t>
+          <t>96444</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>95429</t>
+          <t>94622</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>118700</t>
+          <t>119687</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>180539</t>
+          <t>181761</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>211282</t>
+          <t>210576</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,17%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36416</t>
+          <t>35821</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>21177</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>43814</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45083</t>
+          <t>45682</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71543</t>
+          <t>72191</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22923</t>
+          <t>23113</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31521</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>99270</t>
+          <t>99020</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>113854</t>
+          <t>113934</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>124439</t>
+          <t>123082</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>140508</t>
+          <t>140092</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>228698</t>
+          <t>228774</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>249945</t>
+          <t>250833</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>18741</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>17225</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>33954</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>457389</t>
+          <t>454155</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>559959</t>
+          <t>560814</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>614974</t>
+          <t>614706</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>654875</t>
+          <t>656060</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1078915</t>
+          <t>1095391</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1199255</t>
+          <t>1200342</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>64543</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>95937</t>
+          <t>96166</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>69007</t>
+          <t>67849</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>104579</t>
+          <t>103397</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>141307</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>188818</t>
+          <t>191392</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>135692</t>
+          <t>139205</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>49983</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>62505</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>192037</t>
+          <t>182731</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
